--- a/Result/profitability/3276.xlsx
+++ b/Result/profitability/3276.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.08</v>
       </c>
       <c r="M2" t="n">
-        <v>0.04999999999999998</v>
+        <v>0.04874999999999997</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8387499999999999</v>
+        <v>1.67</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.85</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.06500000000000003</v>
+        <v>-0.06250000000000003</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4449999999999998</v>
+        <v>1.24375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.06</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.06250000000000003</v>
+        <v>-0.05625000000000002</v>
       </c>
       <c r="N4" t="n">
-        <v>2.98375</v>
+        <v>3.64875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.3</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.22625</v>
+        <v>-0.22375</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.813750000000001</v>
+        <v>-0.5650000000000004</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.39</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.28</v>
+        <v>-0.2837500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-4.33375</v>
+        <v>-3.862500000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.34</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.33375</v>
+        <v>-0.335</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.35625</v>
+        <v>-2.77125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.02</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.34</v>
+        <v>-0.3325</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.921250000000001</v>
+        <v>-0.4025000000000003</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>-0.3775000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1825000000000009</v>
+        <v>-0.1825000000000004</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>-0.3975</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7237500000000012</v>
+        <v>-0.7237500000000008</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -9826,6 +9826,135 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3276</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>192</v>
+      </c>
+      <c r="D75" t="n">
+        <v>184</v>
+      </c>
+      <c r="E75" t="n">
+        <v>9</v>
+      </c>
+      <c r="F75" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-7.37%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>17</v>
+      </c>
+      <c r="J75" t="n">
+        <v>3</v>
+      </c>
+      <c r="K75" t="n">
+        <v>4</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.04749999999999997</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-0.6587500000000003</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>13.38709677419355</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-1.806509945750452</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
